--- a/plan_data/开票信息.xlsx
+++ b/plan_data/开票信息.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
   <si>
     <r>
       <rPr>
@@ -175,28 +175,67 @@
     <t>仓库代码</t>
   </si>
   <si>
-    <t>FBA19B58K14J</t>
-  </si>
-  <si>
-    <t>4KQKZPNM</t>
+    <t>FBA19D70W3D0</t>
+  </si>
+  <si>
+    <t>4T4DFE3V</t>
   </si>
   <si>
     <t>是</t>
   </si>
   <si>
+    <t>紐酷</t>
+  </si>
+  <si>
+    <t>AAA</t>
+  </si>
+  <si>
+    <t>CLT2</t>
+  </si>
+  <si>
+    <t>FBA19D712FR3</t>
+  </si>
+  <si>
+    <t>7Y2TTF5V</t>
+  </si>
+  <si>
+    <t>TEB9</t>
+  </si>
+  <si>
+    <t>FBA19D715WGH</t>
+  </si>
+  <si>
+    <t>6V1SG1TE</t>
+  </si>
+  <si>
+    <t>SBD1</t>
+  </si>
+  <si>
+    <t>FBA19D6YR2MZ</t>
+  </si>
+  <si>
+    <t>4LEJV67K</t>
+  </si>
+  <si>
+    <t>LAX9</t>
+  </si>
+  <si>
+    <t>FBA19D6ZXKK1</t>
+  </si>
+  <si>
+    <t>6G8PM5YO</t>
+  </si>
+  <si>
+    <t>LAS1</t>
+  </si>
+  <si>
+    <t>支持物流商</t>
+  </si>
+  <si>
+    <t>赤道</t>
+  </si>
+  <si>
     <t>鹏城海</t>
-  </si>
-  <si>
-    <t>YYZ4</t>
-  </si>
-  <si>
-    <t>支持物流商</t>
-  </si>
-  <si>
-    <t>赤道</t>
-  </si>
-  <si>
-    <t>紐酷</t>
   </si>
   <si>
     <t>易通安达</t>
@@ -1578,67 +1617,147 @@
       <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="13">
+        <v>46157</v>
+      </c>
+      <c r="G3" s="13">
+        <v>46157</v>
+      </c>
+      <c r="H3" s="13">
+        <v>46157</v>
+      </c>
       <c r="I3" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="14"/>
+      <c r="A4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="13">
+        <v>46157</v>
+      </c>
+      <c r="G4" s="13">
+        <v>46157</v>
+      </c>
+      <c r="H4" s="13">
+        <v>46157</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="15"/>
+      <c r="A5" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="13">
+        <v>46157</v>
+      </c>
+      <c r="G5" s="13">
+        <v>46157</v>
+      </c>
+      <c r="H5" s="13">
+        <v>46157</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="10"/>
+      <c r="A6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="13">
+        <v>46157</v>
+      </c>
+      <c r="G6" s="13">
+        <v>46157</v>
+      </c>
+      <c r="H6" s="13">
+        <v>46157</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="10"/>
+      <c r="A7" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="13">
+        <v>46157</v>
+      </c>
+      <c r="G7" s="13">
+        <v>46157</v>
+      </c>
+      <c r="H7" s="13">
+        <v>46157</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C2 C3:C7 C8:C1048576">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D$1:D$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D2 D3:D7 D8:D1048576">
       <formula1>数据字典!$A$2:$A$10</formula1>
     </dataValidation>
   </dataValidations>
@@ -1659,32 +1778,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/plan_data/开票信息.xlsx
+++ b/plan_data/开票信息.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <r>
       <rPr>
@@ -184,64 +184,61 @@
     <t>是</t>
   </si>
   <si>
+    <t>九方</t>
+  </si>
+  <si>
+    <t>AAA</t>
+  </si>
+  <si>
+    <t>CLT2</t>
+  </si>
+  <si>
+    <t>FBA19D712FR3</t>
+  </si>
+  <si>
+    <t>7Y2TTF5V</t>
+  </si>
+  <si>
+    <t>TEB9</t>
+  </si>
+  <si>
+    <t>FBA19D715WGH</t>
+  </si>
+  <si>
+    <t>6V1SG1TE</t>
+  </si>
+  <si>
+    <t>SBD1</t>
+  </si>
+  <si>
+    <t>FBA19D6YR2MZ</t>
+  </si>
+  <si>
+    <t>4LEJV67K</t>
+  </si>
+  <si>
+    <t>LAX9</t>
+  </si>
+  <si>
+    <t>FBA19D6ZXKK1</t>
+  </si>
+  <si>
+    <t>6G8PM5YO</t>
+  </si>
+  <si>
+    <t>LAS1</t>
+  </si>
+  <si>
+    <t>支持物流商</t>
+  </si>
+  <si>
+    <t>赤道</t>
+  </si>
+  <si>
     <t>紐酷</t>
   </si>
   <si>
-    <t>AAA</t>
-  </si>
-  <si>
-    <t>CLT2</t>
-  </si>
-  <si>
-    <t>FBA19D712FR3</t>
-  </si>
-  <si>
-    <t>7Y2TTF5V</t>
-  </si>
-  <si>
-    <t>TEB9</t>
-  </si>
-  <si>
-    <t>FBA19D715WGH</t>
-  </si>
-  <si>
-    <t>6V1SG1TE</t>
-  </si>
-  <si>
-    <t>SBD1</t>
-  </si>
-  <si>
-    <t>FBA19D6YR2MZ</t>
-  </si>
-  <si>
-    <t>4LEJV67K</t>
-  </si>
-  <si>
-    <t>LAX9</t>
-  </si>
-  <si>
-    <t>FBA19D6ZXKK1</t>
-  </si>
-  <si>
-    <t>6G8PM5YO</t>
-  </si>
-  <si>
-    <t>LAS1</t>
-  </si>
-  <si>
-    <t>支持物流商</t>
-  </si>
-  <si>
-    <t>赤道</t>
-  </si>
-  <si>
     <t>鹏城海</t>
-  </si>
-  <si>
-    <t>易通安达</t>
-  </si>
-  <si>
-    <t>壹港</t>
   </si>
 </sst>
 </file>
@@ -1758,7 +1755,7 @@
       <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D2 D3:D7 D8:D1048576">
-      <formula1>数据字典!$A$2:$A$10</formula1>
+      <formula1>数据字典!$A$2:$A$8</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1770,8 +1767,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5"/>
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="12.7692307692308" customWidth="1"/>
   </cols>
@@ -1788,22 +1785,17 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/plan_data/开票信息.xlsx
+++ b/plan_data/开票信息.xlsx
@@ -28,53 +28,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="34">
+  <si>
+    <t>填写说明：
+带*为必填项
+当物流商为【赤道】时，除物流模式外所有业务字段必填
+【紐酷】渠道、送货时间必填
+物流模式当前仅占位，可选 FIST/SEND</t>
+  </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>填写说明：
-带</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>为必填项
-当物流商为【赤道】时，所有信息均是必填
-【紐酷】渠道、送货时间必填</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -91,13 +54,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -113,15 +69,10 @@
     </r>
   </si>
   <si>
+    <t>仓库代码</t>
+  </si>
+  <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -138,13 +89,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -160,6 +104,22 @@
     </r>
   </si>
   <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>物流模式</t>
+    </r>
+  </si>
+  <si>
     <t>渠道类型</t>
   </si>
   <si>
@@ -172,73 +132,73 @@
     <t>货件创建时间</t>
   </si>
   <si>
-    <t>仓库代码</t>
-  </si>
-  <si>
     <t>FBA19D70W3D0</t>
   </si>
   <si>
     <t>4T4DFE3V</t>
   </si>
   <si>
+    <t>CLT2</t>
+  </si>
+  <si>
     <t>是</t>
   </si>
   <si>
+    <t>赤道</t>
+  </si>
+  <si>
+    <t>FIST</t>
+  </si>
+  <si>
+    <t>AAA</t>
+  </si>
+  <si>
+    <t>FBA19D712FR3</t>
+  </si>
+  <si>
+    <t>7Y2TTF5V</t>
+  </si>
+  <si>
+    <t>TEB9</t>
+  </si>
+  <si>
+    <t>FBA19D715WGH</t>
+  </si>
+  <si>
+    <t>6V1SG1TE</t>
+  </si>
+  <si>
+    <t>SBD1</t>
+  </si>
+  <si>
+    <t>FBA19D6YR2MZ</t>
+  </si>
+  <si>
+    <t>4LEJV67K</t>
+  </si>
+  <si>
+    <t>LAX9</t>
+  </si>
+  <si>
+    <t>FBA19D6ZXKK1</t>
+  </si>
+  <si>
+    <t>6G8PM5YO</t>
+  </si>
+  <si>
+    <t>LAS1</t>
+  </si>
+  <si>
+    <t>支持物流商</t>
+  </si>
+  <si>
+    <t>紐酷</t>
+  </si>
+  <si>
+    <t>鹏城海</t>
+  </si>
+  <si>
     <t>九方</t>
-  </si>
-  <si>
-    <t>AAA</t>
-  </si>
-  <si>
-    <t>CLT2</t>
-  </si>
-  <si>
-    <t>FBA19D712FR3</t>
-  </si>
-  <si>
-    <t>7Y2TTF5V</t>
-  </si>
-  <si>
-    <t>TEB9</t>
-  </si>
-  <si>
-    <t>FBA19D715WGH</t>
-  </si>
-  <si>
-    <t>6V1SG1TE</t>
-  </si>
-  <si>
-    <t>SBD1</t>
-  </si>
-  <si>
-    <t>FBA19D6YR2MZ</t>
-  </si>
-  <si>
-    <t>4LEJV67K</t>
-  </si>
-  <si>
-    <t>LAX9</t>
-  </si>
-  <si>
-    <t>FBA19D6ZXKK1</t>
-  </si>
-  <si>
-    <t>6G8PM5YO</t>
-  </si>
-  <si>
-    <t>LAS1</t>
-  </si>
-  <si>
-    <t>支持物流商</t>
-  </si>
-  <si>
-    <t>赤道</t>
-  </si>
-  <si>
-    <t>紐酷</t>
-  </si>
-  <si>
-    <t>鹏城海</t>
   </si>
 </sst>
 </file>
@@ -251,7 +211,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -268,13 +228,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
@@ -433,14 +386,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -648,7 +593,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -694,19 +639,6 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -815,199 +747,194 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1276,11 +1203,6 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <colors>
-    <mruColors>
-      <color rgb="00FF0000"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1547,215 +1469,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultColWidth="10.3846153846154" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="18.6153846153846" customWidth="1"/>
-    <col min="2" max="2" width="12.9230769230769" customWidth="1"/>
-    <col min="3" max="3" width="13.9423076923077" customWidth="1"/>
-    <col min="4" max="4" width="12.1730769230769" customWidth="1"/>
-    <col min="5" max="5" width="29.6923076923077" customWidth="1"/>
-    <col min="6" max="7" width="12.9230769230769" customWidth="1"/>
-    <col min="8" max="8" width="17.625" customWidth="1"/>
-    <col min="9" max="9" width="12.9230769230769" style="3" customWidth="1"/>
+    <col min="1" max="1" width="16.4615384615385" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7692307692308" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.9230769230769" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7692307692308" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7692307692308" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7692307692308" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.8942307692308" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.9230769230769" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.9230769230769" style="4" customWidth="1"/>
+    <col min="10" max="10" width="19" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="94" customHeight="1" spans="1:9">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="94" customHeight="1" spans="1:10">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
     </row>
-    <row r="2" ht="21" spans="1:9">
-      <c r="A2" s="5" t="s">
+    <row r="2" ht="21" customHeight="1" spans="1:10">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="8" t="s">
         <v>9</v>
       </c>
+      <c r="J2" s="9" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="13">
+      <c r="E3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="14">
         <v>46157</v>
       </c>
-      <c r="G3" s="13">
+      <c r="I3" s="14">
         <v>46157</v>
       </c>
-      <c r="H3" s="13">
+      <c r="J3" s="14">
         <v>46157</v>
       </c>
-      <c r="I3" s="14" t="s">
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="F4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="14">
+        <v>46157</v>
+      </c>
+      <c r="I4" s="14">
+        <v>46157</v>
+      </c>
+      <c r="J4" s="14">
+        <v>46157</v>
+      </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="10" t="s">
+    <row r="5" spans="1:10">
+      <c r="A5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="G5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="H5" s="14">
+        <v>46157</v>
+      </c>
+      <c r="I5" s="14">
+        <v>46157</v>
+      </c>
+      <c r="J5" s="14">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="13">
+      <c r="E6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="14">
         <v>46157</v>
       </c>
-      <c r="G4" s="13">
+      <c r="I6" s="14">
         <v>46157</v>
       </c>
-      <c r="H4" s="13">
+      <c r="J6" s="14">
         <v>46157</v>
       </c>
-      <c r="I4" s="14" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2" t="s">
+    <row r="7" spans="1:10">
+      <c r="A7" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="13">
+      <c r="E7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="14">
         <v>46157</v>
       </c>
-      <c r="G5" s="13">
+      <c r="I7" s="14">
         <v>46157</v>
       </c>
-      <c r="H5" s="13">
+      <c r="J7" s="14">
         <v>46157</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="13">
-        <v>46157</v>
-      </c>
-      <c r="G6" s="13">
-        <v>46157</v>
-      </c>
-      <c r="H6" s="13">
-        <v>46157</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="13">
-        <v>46157</v>
-      </c>
-      <c r="G7" s="13">
-        <v>46157</v>
-      </c>
-      <c r="H7" s="13">
-        <v>46157</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C2 C3:C7 C8:C1048576">
+  <dataValidations count="3">
+    <dataValidation type="list" errorTitle="无效是否退税" error="是否退税只允许填写 是 或 否" sqref="D3:D100">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D2 D3:D7 D8:D1048576">
-      <formula1>数据字典!$A$2:$A$8</formula1>
+    <dataValidation type="list" errorTitle="无效物流商" error="物流商必须来自数据字典" sqref="E3:E7 E8:E100">
+      <formula1>数据字典!$A$2:$A$5</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorTitle="无效物流模式" error="物流模式只允许填写 FIST 或 SEND" promptTitle="物流模式" prompt="请选择 FIST 或 SEND；当前字段仅占位，暂不参与业务逻辑。" sqref="F3:F7 F8:F100">
+      <formula1>"FIST,SEND"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1770,32 +1708,32 @@
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="12.7692307692308" customWidth="1"/>
+    <col min="1" max="1" width="12.7692307692308" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>28</v>
+      <c r="A1" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="2" t="s">
-        <v>29</v>
+      <c r="A2" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="2" t="s">
-        <v>30</v>
+      <c r="A3" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="2" t="s">
-        <v>31</v>
+      <c r="A4" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
+      <c r="A5" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/plan_data/开票信息.xlsx
+++ b/plan_data/开票信息.xlsx
@@ -38,6 +38,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -54,6 +62,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -73,6 +89,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -89,6 +113,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -105,6 +137,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -144,61 +184,61 @@
     <t>是</t>
   </si>
   <si>
+    <t>九方</t>
+  </si>
+  <si>
+    <t>SEND</t>
+  </si>
+  <si>
+    <t>AAA</t>
+  </si>
+  <si>
+    <t>FBA19D712FR3</t>
+  </si>
+  <si>
+    <t>7Y2TTF5V</t>
+  </si>
+  <si>
+    <t>TEB9</t>
+  </si>
+  <si>
+    <t>FBA19D715WGH</t>
+  </si>
+  <si>
+    <t>6V1SG1TE</t>
+  </si>
+  <si>
+    <t>SBD1</t>
+  </si>
+  <si>
+    <t>FBA19D6YR2MZ</t>
+  </si>
+  <si>
+    <t>4LEJV67K</t>
+  </si>
+  <si>
+    <t>LAX9</t>
+  </si>
+  <si>
+    <t>FBA19D6ZXKK1</t>
+  </si>
+  <si>
+    <t>6G8PM5YO</t>
+  </si>
+  <si>
+    <t>LAS1</t>
+  </si>
+  <si>
+    <t>支持物流商</t>
+  </si>
+  <si>
     <t>赤道</t>
   </si>
   <si>
-    <t>FIST</t>
-  </si>
-  <si>
-    <t>AAA</t>
-  </si>
-  <si>
-    <t>FBA19D712FR3</t>
-  </si>
-  <si>
-    <t>7Y2TTF5V</t>
-  </si>
-  <si>
-    <t>TEB9</t>
-  </si>
-  <si>
-    <t>FBA19D715WGH</t>
-  </si>
-  <si>
-    <t>6V1SG1TE</t>
-  </si>
-  <si>
-    <t>SBD1</t>
-  </si>
-  <si>
-    <t>FBA19D6YR2MZ</t>
-  </si>
-  <si>
-    <t>4LEJV67K</t>
-  </si>
-  <si>
-    <t>LAX9</t>
-  </si>
-  <si>
-    <t>FBA19D6ZXKK1</t>
-  </si>
-  <si>
-    <t>6G8PM5YO</t>
-  </si>
-  <si>
-    <t>LAS1</t>
-  </si>
-  <si>
-    <t>支持物流商</t>
-  </si>
-  <si>
     <t>紐酷</t>
   </si>
   <si>
     <t>鹏城海</t>
-  </si>
-  <si>
-    <t>九方</t>
   </si>
 </sst>
 </file>
@@ -1718,22 +1758,22 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="3" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/plan_data/开票信息.xlsx
+++ b/plan_data/开票信息.xlsx
@@ -1,435 +1,201 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16160"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="16160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="开票信息" sheetId="1" r:id="rId1"/>
-    <sheet name="数据字典" sheetId="2" r:id="rId2"/>
+    <sheet name="开票信息" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="数据字典" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="34">
-  <si>
-    <t>填写说明：
-带*为必填项
-当物流商为【赤道】时，除物流模式外所有业务字段必填
-【紐酷】渠道、送货时间必填
-物流模式当前仅占位，可选 FIST/SEND</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>货件ID</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>追踪编号</t>
-    </r>
-  </si>
-  <si>
-    <t>仓库代码</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是否退税</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>物流商</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>物流模式</t>
-    </r>
-  </si>
-  <si>
-    <t>渠道类型</t>
-  </si>
-  <si>
-    <t>送货时间</t>
-  </si>
-  <si>
-    <t>预约船期</t>
-  </si>
-  <si>
-    <t>货件创建时间</t>
-  </si>
-  <si>
-    <t>FBA19D70W3D0</t>
-  </si>
-  <si>
-    <t>4T4DFE3V</t>
-  </si>
-  <si>
-    <t>CLT2</t>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>九方</t>
-  </si>
-  <si>
-    <t>SEND</t>
-  </si>
-  <si>
-    <t>AAA</t>
-  </si>
-  <si>
-    <t>FBA19D712FR3</t>
-  </si>
-  <si>
-    <t>7Y2TTF5V</t>
-  </si>
-  <si>
-    <t>TEB9</t>
-  </si>
-  <si>
-    <t>FBA19D715WGH</t>
-  </si>
-  <si>
-    <t>6V1SG1TE</t>
-  </si>
-  <si>
-    <t>SBD1</t>
-  </si>
-  <si>
-    <t>FBA19D6YR2MZ</t>
-  </si>
-  <si>
-    <t>4LEJV67K</t>
-  </si>
-  <si>
-    <t>LAX9</t>
-  </si>
-  <si>
-    <t>FBA19D6ZXKK1</t>
-  </si>
-  <si>
-    <t>6G8PM5YO</t>
-  </si>
-  <si>
-    <t>LAS1</t>
-  </si>
-  <si>
-    <t>支持物流商</t>
-  </si>
-  <si>
-    <t>赤道</t>
-  </si>
-  <si>
-    <t>紐酷</t>
-  </si>
-  <si>
-    <t>鹏城海</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="23">
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="14"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="1"/>
+      <sz val="14"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="0"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -784,196 +550,200 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1221,7 +991,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1230,7 +1000,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1243,11 +1013,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1507,218 +1340,317 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="10.3846153846154" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.3846153846154" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="16.4615384615385" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7692307692308" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.9230769230769" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7692307692308" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7692307692308" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7692307692308" style="1" customWidth="1"/>
-    <col min="7" max="7" width="35.8942307692308" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.9230769230769" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.9230769230769" style="4" customWidth="1"/>
-    <col min="10" max="10" width="19" style="1" customWidth="1"/>
+    <col width="16.4615384615385" customWidth="1" style="1" min="1" max="1"/>
+    <col width="13.7692307692308" customWidth="1" style="1" min="2" max="2"/>
+    <col width="12.9230769230769" customWidth="1" style="1" min="3" max="3"/>
+    <col width="13.7692307692308" customWidth="1" style="1" min="4" max="4"/>
+    <col width="10.7692307692308" customWidth="1" style="1" min="5" max="5"/>
+    <col width="13.7692307692308" customWidth="1" style="1" min="6" max="6"/>
+    <col width="35.8942307692308" customWidth="1" style="1" min="7" max="7"/>
+    <col width="12.9230769230769" customWidth="1" style="1" min="8" max="8"/>
+    <col width="12.9230769230769" customWidth="1" style="4" min="9" max="9"/>
+    <col width="19" customWidth="1" style="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="94" customHeight="1" spans="1:10">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
+    <row r="1" ht="94" customHeight="1" s="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>填写说明：
+带*为必填项
+当物流商为【赤道】时，除物流模式外所有业务字段必填
+【紐酷】渠道、送货时间必填
+物流模式当前仅占位，可选 FIST/SEND</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="21" customHeight="1" spans="1:10">
-      <c r="A2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>10</v>
+    <row r="2" ht="21" customHeight="1" s="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>*货件ID</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>*追踪编号</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>仓库代码</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>*是否退税</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>*物流商</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>物流模式</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>渠道类型</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>送货时间</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>预约船期</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>货件创建时间</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="14">
-        <v>46157</v>
-      </c>
-      <c r="I3" s="14">
-        <v>46157</v>
-      </c>
-      <c r="J3" s="14">
-        <v>46157</v>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>FBA19F25ZHSD</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>2BFZZWNN</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>TEB9</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>联宇</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>SEND</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>黄金鲲运纽约-直送</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="n">
+        <v>46170</v>
+      </c>
+      <c r="I3" s="16" t="n">
+        <v>46175</v>
+      </c>
+      <c r="J3" s="16" t="n">
+        <v>46169</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="14">
-        <v>46157</v>
-      </c>
-      <c r="I4" s="14">
-        <v>46157</v>
-      </c>
-      <c r="J4" s="14">
-        <v>46157</v>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>FBA19F292CTY</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>6CHCUD2W</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>LAS1</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>联宇</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>SEND</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>黄金鲲运-LALB直送</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>46170</v>
+      </c>
+      <c r="I4" s="16" t="n">
+        <v>46175</v>
+      </c>
+      <c r="J4" s="16" t="n">
+        <v>46169</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="14">
-        <v>46157</v>
-      </c>
-      <c r="I5" s="14">
-        <v>46157</v>
-      </c>
-      <c r="J5" s="14">
-        <v>46157</v>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>FBA19F27118M</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>8EFZ6T8A</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>SBD1</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>联宇</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>SEND</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>黄金鲲运-LALB直送</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>46170</v>
+      </c>
+      <c r="I5" s="16" t="n">
+        <v>46175</v>
+      </c>
+      <c r="J5" s="16" t="n">
+        <v>46169</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="14">
-        <v>46157</v>
-      </c>
-      <c r="I6" s="14">
-        <v>46157</v>
-      </c>
-      <c r="J6" s="14">
-        <v>46157</v>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>FBA19F2890KD</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>5RQA5SXX</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>LAX9</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>联宇</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>SEND</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>黄金鲲运-LALB直送</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>46170</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>46175</v>
+      </c>
+      <c r="J6" s="16" t="n">
+        <v>46169</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="14">
-        <v>46157</v>
-      </c>
-      <c r="I7" s="14">
-        <v>46157</v>
-      </c>
-      <c r="J7" s="14">
-        <v>46157</v>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>FBA19F287J5Z</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>7P7KVV2F</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>CLT2</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>联宇</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>SEND</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>黄金鲲运萨凡红-拆派</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>46170</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>46175</v>
+      </c>
+      <c r="J7" s="16" t="n">
+        <v>46169</v>
       </c>
     </row>
   </sheetData>
@@ -1726,58 +1658,76 @@
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" errorTitle="无效是否退税" error="是否退税只允许填写 是 或 否" sqref="D3:D100">
+    <dataValidation sqref="D3:D100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorTitle="无效物流商" error="物流商必须来自数据字典" sqref="E3:E7 E8:E100">
-      <formula1>数据字典!$A$2:$A$5</formula1>
+    <dataValidation sqref="E3:E100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>数据字典!$A$2:$A$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="无效物流模式" error="物流模式只允许填写 FIST 或 SEND" promptTitle="物流模式" prompt="请选择 FIST 或 SEND；当前字段仅占位，暂不参与业务逻辑。" sqref="F3:F7 F8:F100">
+    <dataValidation sqref="F3:F100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"FIST,SEND"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="12.7692307692308" style="1" customWidth="1"/>
+    <col width="12.7692307692308" customWidth="1" style="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="2" t="s">
-        <v>30</v>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>支持物流商</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="3" t="s">
-        <v>31</v>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>赤道</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="3" t="s">
-        <v>32</v>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>紐酷</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="3" t="s">
-        <v>33</v>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>鹏城海</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="3" t="s">
-        <v>15</v>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>九方</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>联宇</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/plan_data/开票信息.xlsx
+++ b/plan_data/开票信息.xlsx
@@ -1,201 +1,364 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="16160" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowHeight="16160"/>
   </bookViews>
   <sheets>
-    <sheet name="开票信息" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="数据字典" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="开票信息" sheetId="1" r:id="rId1"/>
+    <sheet name="数据字典" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+  <si>
+    <t>填写说明：
+带*为必填项
+当物流商为【赤道】时，除物流模式外所有业务字段必填
+【紐酷】渠道、送货时间必填</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>物流模式</t>
+    </r>
+  </si>
+  <si>
+    <t>FIST</t>
+  </si>
+  <si>
+    <t>*货件ID</t>
+  </si>
+  <si>
+    <t>*追踪编号</t>
+  </si>
+  <si>
+    <t>仓库代码</t>
+  </si>
+  <si>
+    <t>*是否退税</t>
+  </si>
+  <si>
+    <t>*物流商</t>
+  </si>
+  <si>
+    <t>渠道类型</t>
+  </si>
+  <si>
+    <t>送货时间</t>
+  </si>
+  <si>
+    <t>预约船期</t>
+  </si>
+  <si>
+    <t>货件创建时间</t>
+  </si>
+  <si>
+    <t>FBA19F25ZHSD</t>
+  </si>
+  <si>
+    <t>2BFZZWNN</t>
+  </si>
+  <si>
+    <t>TEB9</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>联宇</t>
+  </si>
+  <si>
+    <t>黄金鲲运纽约-直送</t>
+  </si>
+  <si>
+    <t>FBA19F292CTY</t>
+  </si>
+  <si>
+    <t>6CHCUD2W</t>
+  </si>
+  <si>
+    <t>LAS1</t>
+  </si>
+  <si>
+    <t>黄金鲲运-LALB直送</t>
+  </si>
+  <si>
+    <t>FBA19F27118M</t>
+  </si>
+  <si>
+    <t>8EFZ6T8A</t>
+  </si>
+  <si>
+    <t>SBD1</t>
+  </si>
+  <si>
+    <t>FBA19F2890KD</t>
+  </si>
+  <si>
+    <t>5RQA5SXX</t>
+  </si>
+  <si>
+    <t>LAX9</t>
+  </si>
+  <si>
+    <t>FBA19F287J5Z</t>
+  </si>
+  <si>
+    <t>7P7KVV2F</t>
+  </si>
+  <si>
+    <t>CLT2</t>
+  </si>
+  <si>
+    <t>黄金鲲运萨凡红-拆派</t>
+  </si>
+  <si>
+    <t>支持物流商</t>
+  </si>
+  <si>
+    <t>赤道</t>
+  </si>
+  <si>
+    <t>紐酷</t>
+  </si>
+  <si>
+    <t>鹏城海</t>
+  </si>
+  <si>
+    <t>九方</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="23">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="14"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="14"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -550,200 +713,206 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -991,7 +1160,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1000,7 +1169,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1013,74 +1182,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1340,394 +1446,275 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="10.3846153846154" defaultRowHeight="16.8" outlineLevelRow="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultColWidth="10.3846153846154" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <cols>
-    <col width="16.4615384615385" customWidth="1" style="1" min="1" max="1"/>
-    <col width="13.7692307692308" customWidth="1" style="1" min="2" max="2"/>
-    <col width="12.9230769230769" customWidth="1" style="1" min="3" max="3"/>
-    <col width="13.7692307692308" customWidth="1" style="1" min="4" max="4"/>
-    <col width="10.7692307692308" customWidth="1" style="1" min="5" max="5"/>
-    <col width="13.7692307692308" customWidth="1" style="1" min="6" max="6"/>
-    <col width="35.8942307692308" customWidth="1" style="1" min="7" max="7"/>
-    <col width="12.9230769230769" customWidth="1" style="1" min="8" max="8"/>
-    <col width="12.9230769230769" customWidth="1" style="4" min="9" max="9"/>
-    <col width="19" customWidth="1" style="1" min="10" max="10"/>
+    <col min="1" max="1" width="16.4615384615385" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7692307692308" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.9230769230769" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7692307692308" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7692307692308" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.8942307692308" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.9230769230769" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.9230769230769" style="4" customWidth="1"/>
+    <col min="9" max="9" width="19" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="94" customHeight="1" s="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>填写说明：
-带*为必填项
-当物流商为【赤道】时，除物流模式外所有业务字段必填
-【紐酷】渠道、送货时间必填
-物流模式当前仅占位，可选 FIST/SEND</t>
-        </is>
-      </c>
+    <row r="1" ht="72" customHeight="1" spans="1:9">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
     </row>
-    <row r="2" ht="21" customHeight="1" s="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>*货件ID</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>*追踪编号</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>仓库代码</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>*是否退税</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>*物流商</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>物流模式</t>
-        </is>
-      </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>渠道类型</t>
-        </is>
-      </c>
-      <c r="H2" s="9" t="inlineStr">
-        <is>
-          <t>送货时间</t>
-        </is>
-      </c>
-      <c r="I2" s="10" t="inlineStr">
-        <is>
-          <t>预约船期</t>
-        </is>
-      </c>
-      <c r="J2" s="9" t="inlineStr">
-        <is>
-          <t>货件创建时间</t>
-        </is>
+    <row r="2" ht="21" customHeight="1" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>FBA19F25ZHSD</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>2BFZZWNN</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>TEB9</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>联宇</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>SEND</t>
-        </is>
-      </c>
-      <c r="G3" s="15" t="inlineStr">
-        <is>
-          <t>黄金鲲运纽约-直送</t>
-        </is>
-      </c>
-      <c r="H3" s="16" t="n">
+    <row r="3" spans="1:9">
+      <c r="A3" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="18">
         <v>46170</v>
       </c>
-      <c r="I3" s="16" t="n">
+      <c r="H3" s="18">
         <v>46175</v>
       </c>
-      <c r="J3" s="16" t="n">
+      <c r="I3" s="18">
         <v>46169</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>FBA19F292CTY</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>6CHCUD2W</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>LAS1</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>联宇</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>SEND</t>
-        </is>
-      </c>
-      <c r="G4" s="15" t="inlineStr">
-        <is>
-          <t>黄金鲲运-LALB直送</t>
-        </is>
-      </c>
-      <c r="H4" s="16" t="n">
+    <row r="4" spans="1:9">
+      <c r="A4" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="18">
         <v>46170</v>
       </c>
-      <c r="I4" s="16" t="n">
+      <c r="H4" s="18">
         <v>46175</v>
       </c>
-      <c r="J4" s="16" t="n">
+      <c r="I4" s="18">
         <v>46169</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>FBA19F27118M</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>8EFZ6T8A</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>SBD1</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>联宇</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>SEND</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>黄金鲲运-LALB直送</t>
-        </is>
-      </c>
-      <c r="H5" s="16" t="n">
+    <row r="5" spans="1:9">
+      <c r="A5" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="18">
         <v>46170</v>
       </c>
-      <c r="I5" s="16" t="n">
+      <c r="H5" s="18">
         <v>46175</v>
       </c>
-      <c r="J5" s="16" t="n">
+      <c r="I5" s="18">
         <v>46169</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>FBA19F2890KD</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>5RQA5SXX</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>LAX9</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>联宇</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>SEND</t>
-        </is>
-      </c>
-      <c r="G6" s="15" t="inlineStr">
-        <is>
-          <t>黄金鲲运-LALB直送</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="n">
+    <row r="6" spans="1:9">
+      <c r="A6" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="18">
         <v>46170</v>
       </c>
-      <c r="I6" s="16" t="n">
+      <c r="H6" s="18">
         <v>46175</v>
       </c>
-      <c r="J6" s="16" t="n">
+      <c r="I6" s="18">
         <v>46169</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>FBA19F287J5Z</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>7P7KVV2F</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>CLT2</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>联宇</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>SEND</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
-        <is>
-          <t>黄金鲲运萨凡红-拆派</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="n">
+    <row r="7" spans="1:9">
+      <c r="A7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="18">
         <v>46170</v>
       </c>
-      <c r="I7" s="16" t="n">
+      <c r="H7" s="18">
         <v>46175</v>
       </c>
-      <c r="J7" s="16" t="n">
+      <c r="I7" s="18">
         <v>46169</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="D3:D100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1">
+      <formula1>"FIST,SEND"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="D3:D100">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation type="list" sqref="E3:E100">
       <formula1>数据字典!$A$2:$A$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="F3:F100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"FIST,SEND"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A6"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5"/>
   <cols>
-    <col width="12.7692307692308" customWidth="1" style="1" min="1" max="1"/>
+    <col min="1" max="1" width="12.7692307692308" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>支持物流商</t>
-        </is>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>赤道</t>
-        </is>
+    <row r="2" spans="1:1">
+      <c r="A2" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>紐酷</t>
-        </is>
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>鹏城海</t>
-        </is>
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>九方</t>
-        </is>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>联宇</t>
-        </is>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/plan_data/开票信息.xlsx
+++ b/plan_data/开票信息.xlsx
@@ -51,7 +51,7 @@
     </r>
   </si>
   <si>
-    <t>FIST</t>
+    <t>SEND</t>
   </si>
   <si>
     <t>*货件ID</t>

--- a/plan_data/开票信息.xlsx
+++ b/plan_data/开票信息.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16160"/>
+    <workbookView windowHeight="16160" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="开票信息" sheetId="1" r:id="rId1"/>
@@ -861,7 +861,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -872,6 +872,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -910,6 +911,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1458,198 +1462,198 @@
     <col min="5" max="5" width="10.7692307692308" style="1" customWidth="1"/>
     <col min="6" max="6" width="35.8942307692308" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.9230769230769" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.9230769230769" style="4" customWidth="1"/>
+    <col min="8" max="8" width="12.9230769230769" style="5" customWidth="1"/>
     <col min="9" max="9" width="19" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="72" customHeight="1" spans="1:9">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="6" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" ht="21" customHeight="1" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="12" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="20">
         <v>46170</v>
       </c>
-      <c r="H3" s="18">
+      <c r="H3" s="20">
         <v>46175</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="20">
         <v>46169</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="20">
         <v>46170</v>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="20">
         <v>46175</v>
       </c>
-      <c r="I4" s="18">
+      <c r="I4" s="20">
         <v>46169</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="20">
         <v>46170</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="20">
         <v>46175</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="20">
         <v>46169</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="20">
         <v>46170</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="20">
         <v>46175</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="20">
         <v>46169</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="20">
         <v>46170</v>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="20">
         <v>46175</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="20">
         <v>46169</v>
       </c>
     </row>
@@ -1677,8 +1681,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5"/>
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="12.7692307692308" style="1" customWidth="1"/>
   </cols>
@@ -1709,9 +1713,21 @@
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="4"/>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="4"/>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/plan_data/开票信息.xlsx
+++ b/plan_data/开票信息.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16160" activeTab="1"/>
+    <workbookView windowHeight="16160"/>
   </bookViews>
   <sheets>
     <sheet name="开票信息" sheetId="1" r:id="rId1"/>
@@ -37,6 +37,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -81,64 +88,64 @@
     <t>货件创建时间</t>
   </si>
   <si>
-    <t>FBA19F25ZHSD</t>
-  </si>
-  <si>
-    <t>2BFZZWNN</t>
+    <t>FBA19FT9Z3XR</t>
+  </si>
+  <si>
+    <t>15UJCFKO</t>
+  </si>
+  <si>
+    <t>LAX9</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>联宇</t>
+  </si>
+  <si>
+    <t>黄金鲲运-LALB-直送</t>
+  </si>
+  <si>
+    <t>FBA19FTD1T0T</t>
+  </si>
+  <si>
+    <t>2Q7VNUSB</t>
   </si>
   <si>
     <t>TEB9</t>
   </si>
   <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>联宇</t>
-  </si>
-  <si>
     <t>黄金鲲运纽约-直送</t>
   </si>
   <si>
-    <t>FBA19F292CTY</t>
-  </si>
-  <si>
-    <t>6CHCUD2W</t>
+    <t>FBA19FTHJSJQ</t>
+  </si>
+  <si>
+    <t>1JQAQY2V</t>
+  </si>
+  <si>
+    <t>SBD1</t>
+  </si>
+  <si>
+    <t>FBA19FTDB56N</t>
+  </si>
+  <si>
+    <t>87UORWXN</t>
   </si>
   <si>
     <t>LAS1</t>
   </si>
   <si>
-    <t>黄金鲲运-LALB直送</t>
-  </si>
-  <si>
-    <t>FBA19F27118M</t>
-  </si>
-  <si>
-    <t>8EFZ6T8A</t>
-  </si>
-  <si>
-    <t>SBD1</t>
-  </si>
-  <si>
-    <t>FBA19F2890KD</t>
-  </si>
-  <si>
-    <t>5RQA5SXX</t>
-  </si>
-  <si>
-    <t>LAX9</t>
-  </si>
-  <si>
-    <t>FBA19F287J5Z</t>
-  </si>
-  <si>
-    <t>7P7KVV2F</t>
+    <t>FBA19FTJ055K</t>
+  </si>
+  <si>
+    <t>8P53HHKY</t>
   </si>
   <si>
     <t>CLT2</t>
   </si>
   <si>
-    <t>黄金鲲运萨凡红-拆派</t>
+    <t>黄金鲲运萨凡纳-直送:</t>
   </si>
   <si>
     <t>支持物流商</t>
@@ -861,7 +868,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -912,10 +919,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1525,20 +1528,20 @@
       <c r="D3" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="20">
-        <v>46170</v>
-      </c>
-      <c r="H3" s="20">
-        <v>46175</v>
-      </c>
-      <c r="I3" s="20">
-        <v>46169</v>
+      <c r="G3" s="18">
+        <v>46184</v>
+      </c>
+      <c r="H3" s="18">
+        <v>46189</v>
+      </c>
+      <c r="I3" s="18">
+        <v>46182</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1554,20 +1557,20 @@
       <c r="D4" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="20">
-        <v>46170</v>
-      </c>
-      <c r="H4" s="20">
-        <v>46175</v>
-      </c>
-      <c r="I4" s="20">
-        <v>46169</v>
+      <c r="G4" s="18">
+        <v>46184</v>
+      </c>
+      <c r="H4" s="18">
+        <v>46189</v>
+      </c>
+      <c r="I4" s="18">
+        <v>46182</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1583,20 +1586,20 @@
       <c r="D5" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="20">
-        <v>46170</v>
-      </c>
-      <c r="H5" s="20">
-        <v>46175</v>
-      </c>
-      <c r="I5" s="20">
-        <v>46169</v>
+      <c r="F5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="18">
+        <v>46184</v>
+      </c>
+      <c r="H5" s="18">
+        <v>46189</v>
+      </c>
+      <c r="I5" s="18">
+        <v>46182</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1612,20 +1615,20 @@
       <c r="D6" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="20">
-        <v>46170</v>
-      </c>
-      <c r="H6" s="20">
-        <v>46175</v>
-      </c>
-      <c r="I6" s="20">
-        <v>46169</v>
+      <c r="F6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="18">
+        <v>46184</v>
+      </c>
+      <c r="H6" s="18">
+        <v>46189</v>
+      </c>
+      <c r="I6" s="18">
+        <v>46182</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1641,20 +1644,20 @@
       <c r="D7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="20">
-        <v>46170</v>
-      </c>
-      <c r="H7" s="20">
-        <v>46175</v>
-      </c>
-      <c r="I7" s="20">
-        <v>46169</v>
+      <c r="G7" s="18">
+        <v>46184</v>
+      </c>
+      <c r="H7" s="18">
+        <v>46189</v>
+      </c>
+      <c r="I7" s="18">
+        <v>46182</v>
       </c>
     </row>
   </sheetData>
